--- a/CJFAS-Submission/Tables/TableA2.xlsx
+++ b/CJFAS-Submission/Tables/TableA2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\CHUMputerVisionProject\ManuscriptSubmission\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\GitHub\chumputer-manuscript\CJFAS-Submission\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFDFC165-0676-4CC1-A8F6-28F95146E46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8FF292-8307-4102-9AAD-53EC3C4443BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31515" yWindow="3555" windowWidth="23415" windowHeight="16860" xr2:uid="{50AD851D-3F03-4C0E-95AA-4F93AFBA487B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{50AD851D-3F03-4C0E-95AA-4F93AFBA487B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,22 +119,67 @@
     <t>Loss</t>
   </si>
   <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>MSE</t>
+  </si>
+  <si>
+    <t>Batching</t>
+  </si>
+  <si>
+    <t>Batch size</t>
+  </si>
+  <si>
+    <t>Scheduling</t>
+  </si>
+  <si>
+    <t>Max epochs</t>
+  </si>
+  <si>
+    <t>Early stopping</t>
+  </si>
+  <si>
+    <t>Patience</t>
+  </si>
+  <si>
+    <t>20 epochs</t>
+  </si>
+  <si>
+    <t>LR on plateau</t>
+  </si>
+  <si>
+    <t>Factor / patience / min LR</t>
+  </si>
+  <si>
+    <t>0.1 / 4 / 1e-12</t>
+  </si>
+  <si>
+    <t>Checkpointing</t>
+  </si>
+  <si>
+    <t>Monitor / policy</t>
+  </si>
+  <si>
+    <t>val_loss, best only</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>Steps per epoch</t>
+  </si>
+  <si>
+    <t>len(x_train) // batch_size</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Mean Squared Error + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ℓ</t>
+      <t>Mean Squared Error + ℓ</t>
     </r>
     <r>
       <rPr>
         <vertAlign val="subscript"/>
-        <sz val="12"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
@@ -142,66 +187,12 @@
       <t>2</t>
     </r>
   </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>MSE</t>
-  </si>
-  <si>
-    <t>Batching</t>
-  </si>
-  <si>
-    <t>Batch size</t>
-  </si>
-  <si>
-    <t>Scheduling</t>
-  </si>
-  <si>
-    <t>Max epochs</t>
-  </si>
-  <si>
-    <t>Early stopping</t>
-  </si>
-  <si>
-    <t>Patience</t>
-  </si>
-  <si>
-    <t>20 epochs</t>
-  </si>
-  <si>
-    <t>LR on plateau</t>
-  </si>
-  <si>
-    <t>Factor / patience / min LR</t>
-  </si>
-  <si>
-    <t>0.1 / 4 / 1e-12</t>
-  </si>
-  <si>
-    <t>Checkpointing</t>
-  </si>
-  <si>
-    <t>Monitor / policy</t>
-  </si>
-  <si>
-    <t>val_loss, best only</t>
-  </si>
-  <si>
-    <t>Steps</t>
-  </si>
-  <si>
-    <t>Steps per epoch</t>
-  </si>
-  <si>
-    <t>len(x_train) // batch_size</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,26 +202,20 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <vertAlign val="subscript"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -619,7 +604,7 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="31.7109375" customWidth="1"/>
+    <col min="1" max="3" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -633,7 +618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -655,7 +640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -721,7 +706,7 @@
         <v>6.9999999999999994E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -729,7 +714,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -737,18 +722,18 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C12" s="2">
         <v>16</v>
@@ -756,10 +741,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C13" s="2">
         <v>150</v>
@@ -767,46 +752,46 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/CJFAS-Submission/Tables/TableA2.xlsx
+++ b/CJFAS-Submission/Tables/TableA2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\GitHub\chumputer-manuscript\CJFAS-Submission\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8FF292-8307-4102-9AAD-53EC3C4443BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3317CB1E-A332-4234-B8CB-F8E23D638D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{50AD851D-3F03-4C0E-95AA-4F93AFBA487B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FCB07297-B30E-4E81-98A7-90071D94F4A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>Category</t>
   </si>
@@ -47,13 +47,16 @@
     <t>Phase 1</t>
   </si>
   <si>
+    <t>Phase 2: Fine-tuning</t>
+  </si>
+  <si>
     <t>Model backbone</t>
   </si>
   <si>
     <t>Architecture</t>
   </si>
   <si>
-    <t>EfficientNet V1.1.0, also called EfficientNetB4</t>
+    <t>EfficientNetV2L, NASNetLarge, and ConvNeXtLarge (pretrained)</t>
   </si>
   <si>
     <t>Input</t>
@@ -62,7 +65,7 @@
     <t>Input shape</t>
   </si>
   <si>
-    <t>(380, 380, 3)</t>
+    <t>(512, 512, 3)</t>
   </si>
   <si>
     <t>Distribution</t>
@@ -83,13 +86,25 @@
     <t xml:space="preserve">First ⅓ of the network </t>
   </si>
   <si>
+    <t>All layers unfrozen</t>
+  </si>
+  <si>
     <t>Model head</t>
   </si>
   <si>
     <t>Pooling</t>
   </si>
   <si>
-    <t>Flatted</t>
+    <t>GlobalAveragePooling2D</t>
+  </si>
+  <si>
+    <t>Dense layer</t>
+  </si>
+  <si>
+    <t>4096 units, ReLU</t>
+  </si>
+  <si>
+    <t>Dropout</t>
   </si>
   <si>
     <t>Output</t>
@@ -113,6 +128,9 @@
     <t>Learning rate</t>
   </si>
   <si>
+    <t>1e-5 (= LR × 0.1)</t>
+  </si>
+  <si>
     <t>Loss/Metric</t>
   </si>
   <si>
@@ -137,13 +155,22 @@
     <t>Max epochs</t>
   </si>
   <si>
+    <t>80 - 150</t>
+  </si>
+  <si>
+    <t>Remaining epochs after phase 1</t>
+  </si>
+  <si>
+    <t>Max initial epochs</t>
+  </si>
+  <si>
     <t>Early stopping</t>
   </si>
   <si>
     <t>Patience</t>
   </si>
   <si>
-    <t>20 epochs</t>
+    <t>9 epochs</t>
   </si>
   <si>
     <t>LR on plateau</t>
@@ -600,14 +627,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FBAC18B-07F1-4D7C-8EF8-A085003BF69F}">
-  <dimension ref="A1:C17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35987FDF-3080-4EA3-B63F-952081B533E1}">
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="28.42578125" customWidth="1"/>
+    <col min="1" max="4" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,173 +644,197 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3">
-        <v>6.9999999999999994E-5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1E-4</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="2">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="2">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
@@ -793,6 +844,43 @@
       <c r="C17" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
